--- a/sporting-martinus/2026_2027-SPM4-trainingsschema.xlsx
+++ b/sporting-martinus/2026_2027-SPM4-trainingsschema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/siebeld/Desktop/CodingAdventures/sporting-martinus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Siebe\Desktop\CodingAdventures\sporting-martinus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E47714A-149B-784E-8B5B-0EDF0FD93925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC00261-948B-4BC0-8C93-1CF6A70788D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="3080" windowWidth="28040" windowHeight="17180" xr2:uid="{0F084BDD-1696-3941-BC4E-0EF4FFF1CBE3}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{0F084BDD-1696-3941-BC4E-0EF4FFF1CBE3}"/>
   </bookViews>
   <sheets>
     <sheet name="2026_2027-SPM4-trainingsschema" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Steven</t>
+  </si>
+  <si>
+    <t>Willem</t>
   </si>
 </sst>
 </file>
@@ -583,24 +586,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -616,7 +619,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -933,9 +936,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D26B24-098A-7448-BC33-DF2BF3D9A0A2}">
   <dimension ref="A1:B36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -943,7 +946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46267</v>
       </c>
@@ -951,7 +954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46281</v>
       </c>
@@ -959,7 +962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46288</v>
       </c>
@@ -967,7 +970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46295</v>
       </c>
@@ -975,7 +978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46302</v>
       </c>
@@ -983,7 +986,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46309</v>
       </c>
@@ -991,7 +994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46316</v>
       </c>
@@ -999,7 +1002,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46323</v>
       </c>
@@ -1007,7 +1010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46330</v>
       </c>
@@ -1015,7 +1018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46337</v>
       </c>
@@ -1023,7 +1026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46344</v>
       </c>
@@ -1031,7 +1034,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46351</v>
       </c>
@@ -1039,7 +1042,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46358</v>
       </c>
@@ -1047,7 +1050,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46365</v>
       </c>
@@ -1055,7 +1058,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46400</v>
       </c>
@@ -1063,7 +1066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46407</v>
       </c>
@@ -1071,7 +1074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46414</v>
       </c>
@@ -1079,7 +1082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46421</v>
       </c>
@@ -1087,7 +1090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46428</v>
       </c>
@@ -1095,7 +1098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46435</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46442</v>
       </c>
@@ -1111,7 +1114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46449</v>
       </c>
@@ -1119,7 +1122,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46456</v>
       </c>
@@ -1127,7 +1130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46463</v>
       </c>
@@ -1135,7 +1138,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46470</v>
       </c>
@@ -1143,84 +1146,84 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46477</v>
       </c>
       <c r="B27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46484</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46491</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46498</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46505</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46512</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46519</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46526</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46533</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46540</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/sporting-martinus/2026_2027-SPM4-trainingsschema.xlsx
+++ b/sporting-martinus/2026_2027-SPM4-trainingsschema.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/siebeld/Desktop/CodingAdventures/sporting-martinus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E47714A-149B-784E-8B5B-0EDF0FD93925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D93B979-61CF-9A49-894D-B72873659242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="3080" windowWidth="28040" windowHeight="17180" xr2:uid="{0F084BDD-1696-3941-BC4E-0EF4FFF1CBE3}"/>
+    <workbookView xWindow="6960" yWindow="2160" windowWidth="28040" windowHeight="17180" xr2:uid="{0F084BDD-1696-3941-BC4E-0EF4FFF1CBE3}"/>
   </bookViews>
   <sheets>
     <sheet name="2026_2027-SPM4-trainingsschema" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -71,6 +84,9 @@
   </si>
   <si>
     <t>Steven</t>
+  </si>
+  <si>
+    <t>Paul</t>
   </si>
 </sst>
 </file>
@@ -934,6 +950,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D26B24-098A-7448-BC33-DF2BF3D9A0A2}">
   <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -972,7 +992,7 @@
         <v>46295</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1084,7 +1104,7 @@
         <v>46421</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">

--- a/sporting-martinus/2026_2027-SPM4-trainingsschema.xlsx
+++ b/sporting-martinus/2026_2027-SPM4-trainingsschema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/siebeld/Desktop/CodingAdventures/sporting-martinus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D93B979-61CF-9A49-894D-B72873659242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AC9C10-B1C0-E645-9E60-7B839E115E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6960" yWindow="2160" windowWidth="28040" windowHeight="17180" xr2:uid="{0F084BDD-1696-3941-BC4E-0EF4FFF1CBE3}"/>
   </bookViews>
@@ -1112,7 +1112,7 @@
         <v>46428</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
